--- a/fuction_ensemble_1/redes-ensemble-s/Teste02 copy/content/results/metrics_1_4.xlsx
+++ b/fuction_ensemble_1/redes-ensemble-s/Teste02 copy/content/results/metrics_1_4.xlsx
@@ -513,661 +513,661 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_1_4_6</t>
+          <t>model_1_4_0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8083944779168645</v>
+        <v>0.383139888910207</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3871801040110363</v>
+        <v>-0.1890382956260672</v>
       </c>
       <c r="D2" t="n">
-        <v>0.993563988251529</v>
+        <v>0.03557487410794224</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.249839193449548</v>
+        <v>0.1813824127307416</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9221879680406688</v>
+        <v>0.1275419117392403</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1137453148361305</v>
+        <v>0.3661948089122145</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3637963627001575</v>
+        <v>0.705864496063535</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004711795595943966</v>
+        <v>0.5431539326309121</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06455891868713967</v>
+        <v>0.7736512230022802</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03463535714154182</v>
+        <v>0.6584025778165961</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1812593621253176</v>
+        <v>0.3389993702210757</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3372614932602453</v>
+        <v>0.60514032167111</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4890519411116386</v>
+        <v>-0.6449602962394478</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3516194132558705</v>
+        <v>0.6309023979778062</v>
       </c>
       <c r="P2" t="n">
-        <v>34.34758682050627</v>
+        <v>32.00917964479191</v>
       </c>
       <c r="Q2" t="n">
-        <v>52.63072419352928</v>
+        <v>50.29231701781492</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_1_4_5</t>
+          <t>model_1_4_2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8081804825041988</v>
+        <v>0.3683946869325674</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3858662213504439</v>
+        <v>-0.3500787186053795</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9936607398500645</v>
+        <v>0.01027147551462937</v>
       </c>
       <c r="E3" t="n">
-        <v>-4.187971044281025</v>
+        <v>0.1245020017680014</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9231221563245695</v>
+        <v>0.08248368626095282</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1138723517572093</v>
+        <v>0.3749481977657009</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3645763402042608</v>
+        <v>0.8014650477281039</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004640963880015499</v>
+        <v>0.5574045365253025</v>
       </c>
       <c r="J3" t="n">
-        <v>0.06379810665760587</v>
+        <v>0.8274072138221086</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03421953526881068</v>
+        <v>0.6924058751737056</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1807746090864768</v>
+        <v>0.337126015921887</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3374497766441834</v>
+        <v>0.6123301378878071</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4884812866778636</v>
+        <v>-0.6842808348464868</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3518157122532632</v>
+        <v>0.6383982995558195</v>
       </c>
       <c r="P3" t="n">
-        <v>34.34535435874405</v>
+        <v>31.9619348036906</v>
       </c>
       <c r="Q3" t="n">
-        <v>52.62849173176706</v>
+        <v>50.24507217671361</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_1_4_3</t>
+          <t>model_1_4_1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8077314931656676</v>
+        <v>0.3735036938213083</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3851341964740854</v>
+        <v>-0.3526512154538237</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9931124174878795</v>
+        <v>0.02000877313219451</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.184204091251426</v>
+        <v>0.1425592668316901</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9227232682770554</v>
+        <v>0.09742389487426462</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1141388912238909</v>
+        <v>0.3719152705789382</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3650109017926953</v>
+        <v>0.802992192983418</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005042389948250209</v>
+        <v>0.5519205944833673</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06375178325504535</v>
+        <v>0.8103418277152693</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03439708660164778</v>
+        <v>0.6811312110993183</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1819936792715508</v>
+        <v>0.3371777735149648</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3378444778650243</v>
+        <v>0.6098485636442363</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4872839817751137</v>
+        <v>-0.670656816476511</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3522272167222196</v>
+        <v>0.6358110795591331</v>
       </c>
       <c r="P4" t="n">
-        <v>34.34067845619457</v>
+        <v>31.97817843582562</v>
       </c>
       <c r="Q4" t="n">
-        <v>52.62381582921758</v>
+        <v>50.26131580884864</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_1_4_4</t>
+          <t>model_1_4_3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.807903322856148</v>
+        <v>0.364908209737397</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3848095567650021</v>
+        <v>-0.3854509744962871</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9932614976027581</v>
+        <v>0.003906720859663371</v>
       </c>
       <c r="E5" t="n">
-        <v>-4.228564679174211</v>
+        <v>0.1124710155925973</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9222330870661456</v>
+        <v>0.0725753558493718</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1140368856969656</v>
+        <v>0.3770179212367268</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3652036219477124</v>
+        <v>0.8224635468268393</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004933248595471475</v>
+        <v>0.5609890983832052</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06429729931431706</v>
+        <v>0.8387773423329969</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03461527395489427</v>
+        <v>0.6998832203581011</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1818355390222011</v>
+        <v>0.3356484019340173</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3376934789079671</v>
+        <v>0.614017850910482</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4877421942830613</v>
+        <v>-0.6935781073669411</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3520697894269495</v>
+        <v>0.6401578620159172</v>
       </c>
       <c r="P5" t="n">
-        <v>34.34246664835234</v>
+        <v>31.95092511245401</v>
       </c>
       <c r="Q5" t="n">
-        <v>52.62560402137535</v>
+        <v>50.23406248547702</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_1_4_0</t>
+          <t>model_1_4_4</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8028737813401188</v>
+        <v>0.3632361172566608</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3841100484820557</v>
+        <v>-0.4081736539674945</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9879230992451516</v>
+        <v>0.0002513896750113709</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.294914435486678</v>
+        <v>0.1061380688924648</v>
       </c>
       <c r="F6" t="n">
-        <v>0.930740038724622</v>
+        <v>0.0672459327271514</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1170226388057613</v>
+        <v>0.3780105475639259</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3656188802816538</v>
+        <v>0.8359527109295917</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008841482895500618</v>
+        <v>0.5630477418742442</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05281590951486189</v>
+        <v>0.8447624225902017</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03082869620518125</v>
+        <v>0.703905082232223</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1877471242347691</v>
+        <v>0.3344923451982509</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3420857185059927</v>
+        <v>0.6148256237047428</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4743300835736501</v>
+        <v>-0.6980370206489044</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3566490157578525</v>
+        <v>0.6410000233703499</v>
       </c>
       <c r="P6" t="n">
-        <v>34.29077573767122</v>
+        <v>31.94566636028716</v>
       </c>
       <c r="Q6" t="n">
-        <v>52.57391311069423</v>
+        <v>50.22880373331017</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_1_4_1</t>
+          <t>model_1_4_5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8025128060978034</v>
+        <v>0.359619544612563</v>
       </c>
       <c r="C7" t="n">
-        <v>0.378860811173111</v>
+        <v>-0.435066446409325</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9879334401667932</v>
+        <v>-0.005437835002164881</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.459588977365671</v>
+        <v>0.09515001065999784</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9284737921088035</v>
+        <v>0.05824271544366189</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1172369293029182</v>
+        <v>0.380157501313266</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3687350543034882</v>
+        <v>0.8519174342312066</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008833912320592932</v>
+        <v>0.5662518524620629</v>
       </c>
       <c r="J7" t="n">
-        <v>0.05484096399124908</v>
+        <v>0.8551469108081078</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03183743815592101</v>
+        <v>0.7106993816350853</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1881669273918265</v>
+        <v>0.3332896431479426</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3423987869472061</v>
+        <v>0.6165691374965715</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4733674829274758</v>
+        <v>-0.7076812143664988</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3569754121707493</v>
+        <v>0.6428177621538679</v>
       </c>
       <c r="P7" t="n">
-        <v>34.2871167100608</v>
+        <v>31.93433926998691</v>
       </c>
       <c r="Q7" t="n">
-        <v>52.57025408308381</v>
+        <v>50.21747664300992</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_1_4_7</t>
+          <t>model_1_4_6</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8081916164719453</v>
+        <v>0.3579446223668559</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3719311741568786</v>
+        <v>-0.4621185122848992</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9937961968296917</v>
+        <v>-0.008571649950252835</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.102643105520658</v>
+        <v>0.08960141597160975</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9105986245285338</v>
+        <v>0.05359902540734551</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1138657421529926</v>
+        <v>0.3811518075111914</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3728487861810562</v>
+        <v>0.8679767091233459</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004541796006339899</v>
+        <v>0.5680167835774951</v>
       </c>
       <c r="J8" t="n">
-        <v>0.07504611579675197</v>
+        <v>0.8603907232223205</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03979395590154593</v>
+        <v>0.7142037533999077</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1822247125233212</v>
+        <v>0.3322729262538726</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3374399830384547</v>
+        <v>0.6173749326877399</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4885109772585208</v>
+        <v>-0.7121476736883843</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3518055017134631</v>
+        <v>0.6436578617145503</v>
       </c>
       <c r="P8" t="n">
-        <v>34.34547045006816</v>
+        <v>31.92911507660454</v>
       </c>
       <c r="Q8" t="n">
-        <v>52.62860782309117</v>
+        <v>50.21225244962754</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_1_4_8</t>
+          <t>model_1_4_7</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8082650458276308</v>
+        <v>0.3573672726087949</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3662550336331508</v>
+        <v>-0.4880884383311443</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9939673100096226</v>
+        <v>-0.01018153102039787</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.501984690655854</v>
+        <v>0.08698144669577079</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9052229919129114</v>
+        <v>0.05135777949410159</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1138221513154747</v>
+        <v>0.3814945472677874</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3762183883924444</v>
+        <v>0.8833935790667887</v>
       </c>
       <c r="I9" t="n">
-        <v>0.004416524276095147</v>
+        <v>0.568923451405657</v>
       </c>
       <c r="J9" t="n">
-        <v>0.07995694448562014</v>
+        <v>0.8628667785453471</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04218673438085764</v>
+        <v>0.7158951149755021</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1827415365096328</v>
+        <v>0.3313818078977831</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3373753863509825</v>
+        <v>0.6176524486050285</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4887067888736822</v>
+        <v>-0.7136872730432136</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3517381550112716</v>
+        <v>0.643947192058975</v>
       </c>
       <c r="P9" t="n">
-        <v>34.34623624990734</v>
+        <v>31.92731744247164</v>
       </c>
       <c r="Q9" t="n">
-        <v>52.62937362293035</v>
+        <v>50.21045481549464</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_1_4_9</t>
+          <t>model_1_4_8</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8075018319556831</v>
+        <v>0.3573007905007805</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3563060094150438</v>
+        <v>-0.5174232916467645</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9938973242428183</v>
+        <v>-0.01102933522189664</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.238000322707624</v>
+        <v>0.08575317166489815</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8949984014536738</v>
+        <v>0.05027232568954765</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1142752280389854</v>
+        <v>0.3815340139189823</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3821245589437809</v>
+        <v>0.9008080151946221</v>
       </c>
       <c r="I10" t="n">
-        <v>0.004467760762399852</v>
+        <v>0.5694009256789648</v>
       </c>
       <c r="J10" t="n">
-        <v>0.08900795949601935</v>
+        <v>0.8640275848786041</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0467378601292096</v>
+        <v>0.7167142552787845</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1838373022532785</v>
+        <v>0.3306905984566887</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3380461921675578</v>
+        <v>0.6176843966937988</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4866715518818218</v>
+        <v>-0.7138645586645853</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3524375184202181</v>
+        <v>0.643980500244026</v>
       </c>
       <c r="P10" t="n">
-        <v>34.33829091847623</v>
+        <v>31.92711054771966</v>
       </c>
       <c r="Q10" t="n">
-        <v>52.62142829149924</v>
+        <v>50.21024792074267</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_1_4_10</t>
+          <t>model_1_4_11</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8086678186978616</v>
+        <v>0.3769871126185638</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3527738350602416</v>
+        <v>-0.5193966900769484</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9954046530778682</v>
+        <v>0.009722988827391754</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.87789284816141</v>
+        <v>0.143379111071342</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8873987531032922</v>
+        <v>0.09409916319251954</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1135830479408236</v>
+        <v>0.3698473627050305</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3842214102227788</v>
+        <v>0.9019795097491528</v>
       </c>
       <c r="I11" t="n">
-        <v>0.003364247337596822</v>
+        <v>0.5577134383707343</v>
       </c>
       <c r="J11" t="n">
-        <v>0.09687691852448344</v>
+        <v>0.8095670172194505</v>
       </c>
       <c r="K11" t="n">
-        <v>0.05012058293104013</v>
+        <v>0.6836402277950925</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1825792867520027</v>
+        <v>0.3311706527689906</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3370208419976777</v>
+        <v>0.6081507730037269</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4897808498609644</v>
+        <v>-0.6613676996838298</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3513685169708387</v>
+        <v>0.6340410104561459</v>
       </c>
       <c r="P11" t="n">
-        <v>34.35044201940681</v>
+        <v>31.98932978337751</v>
       </c>
       <c r="Q11" t="n">
-        <v>52.63357939242982</v>
+        <v>50.27246715640052</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_1_4_2</t>
+          <t>model_1_4_9</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7990915679892272</v>
+        <v>0.3603689411955699</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3512788295721276</v>
+        <v>-0.5915111281229741</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9866584067799452</v>
+        <v>-0.008427477051204502</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.611374795558648</v>
+        <v>0.09376492476549103</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9115149187580501</v>
+        <v>0.05625985673408862</v>
       </c>
       <c r="G12" t="n">
-        <v>0.11926792403396</v>
+        <v>0.3797126271293463</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3851089100613977</v>
+        <v>0.9447897553547923</v>
       </c>
       <c r="I12" t="n">
-        <v>0.009767362558352186</v>
+        <v>0.5679355869402503</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0690048353483948</v>
+        <v>0.8564559144416883</v>
       </c>
       <c r="K12" t="n">
-        <v>0.03938609895337349</v>
+        <v>0.7121957506909693</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1916772123176377</v>
+        <v>0.3300780371428916</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3453518843642814</v>
+        <v>0.6162082660345821</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4642441813046059</v>
+        <v>-0.70568282347848</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3600542290586239</v>
+        <v>0.6424415276466346</v>
       </c>
       <c r="P12" t="n">
-        <v>34.25276570828822</v>
+        <v>31.93668111351041</v>
       </c>
       <c r="Q12" t="n">
-        <v>52.53590308131123</v>
+        <v>50.21981848653342</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_1_4_11</t>
+          <t>model_1_4_10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8069557916111348</v>
+        <v>0.3608742025179342</v>
       </c>
       <c r="C13" t="n">
-        <v>0.340924020726881</v>
+        <v>-0.6248465707906032</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9940723367105194</v>
+        <v>-0.008283037689876815</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.593643841678736</v>
+        <v>0.09407738497211926</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8764159890620047</v>
+        <v>0.05650940446954444</v>
       </c>
       <c r="G13" t="n">
-        <v>0.114599381175224</v>
+        <v>0.3794126821822382</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3912559718963874</v>
+        <v>0.9645791141384397</v>
       </c>
       <c r="I13" t="n">
-        <v>0.004339634368791972</v>
+        <v>0.567854240234295</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1056787329206997</v>
+        <v>0.8561606175597781</v>
       </c>
       <c r="K13" t="n">
-        <v>0.05500918364474583</v>
+        <v>0.7120074288970366</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1840878402695452</v>
+        <v>0.3295446368038242</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3385253035966795</v>
+        <v>0.6159648384301154</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4852154442963597</v>
+        <v>-0.7043354599521754</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3529370266147748</v>
+        <v>0.6421877368250812</v>
       </c>
       <c r="P13" t="n">
-        <v>34.33262574916647</v>
+        <v>31.93826159019345</v>
       </c>
       <c r="Q13" t="n">
-        <v>52.61576312218948</v>
+        <v>50.22139896321645</v>
       </c>
     </row>
     <row r="14">
@@ -1177,107 +1177,107 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8072528835871474</v>
+        <v>0.3772312435828993</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3389314386982113</v>
+        <v>-0.6617231095541054</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9942912751678341</v>
+        <v>0.00930797086959434</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.973345615383034</v>
+        <v>0.1440764868530191</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8713509832569637</v>
+        <v>0.09438097208306506</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1144230145445578</v>
+        <v>0.3697024360186923</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3924388546636676</v>
+        <v>0.9864706205319838</v>
       </c>
       <c r="I14" t="n">
-        <v>0.004179349816918155</v>
+        <v>0.5579471720529438</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1103480446901963</v>
+        <v>0.8089079480340615</v>
       </c>
       <c r="K14" t="n">
-        <v>0.05726369725355721</v>
+        <v>0.6834275600435026</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1837074080471066</v>
+        <v>0.330488463518838</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3382647107585386</v>
+        <v>0.6080316077464167</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4860076895657265</v>
+        <v>-0.6607166837789351</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3526653398000128</v>
+        <v>0.633916772087126</v>
       </c>
       <c r="P14" t="n">
-        <v>34.33570608836169</v>
+        <v>31.99011364776876</v>
       </c>
       <c r="Q14" t="n">
-        <v>52.6188434613847</v>
+        <v>50.27325102079177</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_1_4_16</t>
+          <t>model_1_4_14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8081197111298964</v>
+        <v>0.3736122618642636</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3369341949481118</v>
+        <v>-0.9045617990219144</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9948172520995088</v>
+        <v>0.003596958469015976</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.664117035504114</v>
+        <v>0.1319941961083891</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8622414801262195</v>
+        <v>0.08468445722716522</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1139084282701818</v>
+        <v>0.3718508198987447</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3936245048301643</v>
+        <v>1.13063015668525</v>
       </c>
       <c r="I15" t="n">
-        <v>0.003794282808483653</v>
+        <v>0.5611635532539301</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1188426774398318</v>
+        <v>0.8203265629729775</v>
       </c>
       <c r="K15" t="n">
-        <v>0.06131848012415775</v>
+        <v>0.6907450581134538</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1820480088084909</v>
+        <v>0.3350811938004791</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3375032270515081</v>
+        <v>0.6097957198101219</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4883192296797239</v>
+        <v>-0.6703673016952971</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3518714381550854</v>
+        <v>0.6357559860535985</v>
       </c>
       <c r="P15" t="n">
-        <v>34.34472082832467</v>
+        <v>31.97852505383459</v>
       </c>
       <c r="Q15" t="n">
-        <v>52.62785820134768</v>
+        <v>50.2616624268576</v>
       </c>
     </row>
     <row r="16">
@@ -1287,602 +1287,602 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8069470780363055</v>
+        <v>0.3731618394202048</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3361786080776616</v>
+        <v>-0.9116447282612172</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9938330324833936</v>
+        <v>0.004203668457801846</v>
       </c>
       <c r="E16" t="n">
-        <v>-8.292702679872706</v>
+        <v>0.1306519301188374</v>
       </c>
       <c r="F16" t="n">
-        <v>0.866562663268424</v>
+        <v>0.0840703710329016</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1146045539296495</v>
+        <v>0.3721182101187745</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3940730538361168</v>
+        <v>1.134834889448312</v>
       </c>
       <c r="I16" t="n">
-        <v>0.004514828673514909</v>
+        <v>0.5608218606667832</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1142752786489578</v>
+        <v>0.8215950987833003</v>
       </c>
       <c r="K16" t="n">
-        <v>0.05939505366123636</v>
+        <v>0.6912084797250417</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1843584014360944</v>
+        <v>0.3353470368346418</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3385329436401271</v>
+        <v>0.6100149261442498</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4851922080968147</v>
+        <v>-0.6715684282127872</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3529449919106891</v>
+        <v>0.6359845244551898</v>
       </c>
       <c r="P16" t="n">
-        <v>34.33253547577</v>
+        <v>31.97708741210084</v>
       </c>
       <c r="Q16" t="n">
-        <v>52.61567284879301</v>
+        <v>50.26022478512385</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_1_4_14</t>
+          <t>model_1_4_15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8069977898792308</v>
+        <v>0.3730755256796369</v>
       </c>
       <c r="C17" t="n">
-        <v>0.335925063581535</v>
+        <v>-1.022363738295089</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9938657662008227</v>
+        <v>0.002436277673081633</v>
       </c>
       <c r="E17" t="n">
-        <v>-8.380447078272784</v>
+        <v>0.1296300523464439</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8653775151516544</v>
+        <v>0.08277101648569685</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1145744491890515</v>
+        <v>0.3721694496837351</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3942235688015695</v>
+        <v>1.200562476616615</v>
       </c>
       <c r="I17" t="n">
-        <v>0.004490864362750925</v>
+        <v>0.5618172362842823</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1153542990289783</v>
+        <v>0.8225608451838977</v>
       </c>
       <c r="K17" t="n">
-        <v>0.05992258169586464</v>
+        <v>0.69218904073409</v>
       </c>
       <c r="L17" t="n">
-        <v>0.184188823499824</v>
+        <v>0.3344907223009542</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3384884771880005</v>
+        <v>0.6100569233143208</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4853274396779488</v>
+        <v>-0.6717985981876349</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3528986324296371</v>
+        <v>0.6360283095317369</v>
       </c>
       <c r="P17" t="n">
-        <v>34.33306091205101</v>
+        <v>31.97681203703924</v>
       </c>
       <c r="Q17" t="n">
-        <v>52.61619828507402</v>
+        <v>50.25994941006225</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_1_4_15</t>
+          <t>model_1_4_16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8069297393855025</v>
+        <v>0.3716007076989662</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3354633967985591</v>
+        <v>-1.044585135576275</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9938332064520442</v>
+        <v>0.0003849656123122713</v>
       </c>
       <c r="E18" t="n">
-        <v>-8.436802337064771</v>
+        <v>0.1246830798531134</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8645722691952479</v>
+        <v>0.07890797022484575</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1146148469017569</v>
+        <v>0.3730449653458806</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3944976341469106</v>
+        <v>1.213754057957107</v>
       </c>
       <c r="I18" t="n">
-        <v>0.004514701311298376</v>
+        <v>0.5629725133326996</v>
       </c>
       <c r="J18" t="n">
-        <v>0.116047317316945</v>
+        <v>0.8272360822898956</v>
       </c>
       <c r="K18" t="n">
-        <v>0.06028100931412168</v>
+        <v>0.6951042978112976</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1841610542282193</v>
+        <v>0.3338805478511759</v>
       </c>
       <c r="M18" t="n">
-        <v>0.338548145618547</v>
+        <v>0.6107740706234022</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4851459716946733</v>
+        <v>-0.6757314461360899</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3529608410688027</v>
+        <v>0.6367759872864655</v>
       </c>
       <c r="P18" t="n">
-        <v>34.33235585795271</v>
+        <v>31.97211263215761</v>
       </c>
       <c r="Q18" t="n">
-        <v>52.61549323097572</v>
+        <v>50.25525000518061</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_1_4_24</t>
+          <t>model_1_4_17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7744018019298541</v>
+        <v>0.3732552708126332</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3304413102647933</v>
+        <v>-1.227964277926606</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9910951883095548</v>
+        <v>0.001585082923520997</v>
       </c>
       <c r="E19" t="n">
-        <v>-21.77101383977431</v>
+        <v>0.1295519924544667</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6781269483657046</v>
+        <v>0.08240451934417925</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1339248357091637</v>
+        <v>0.3720627452082029</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3974789616561962</v>
+        <v>1.322615838422744</v>
       </c>
       <c r="I19" t="n">
-        <v>0.006519200732614965</v>
+        <v>0.5622966200780537</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2800222972048353</v>
+        <v>0.8226346172745964</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1432707489687251</v>
+        <v>0.6924656186763252</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1914987843369521</v>
+        <v>0.3332453169713624</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3659574233557282</v>
+        <v>0.6099694625210371</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3984048051462776</v>
+        <v>-0.671319277832978</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3815369885042826</v>
+        <v>0.6359371253514144</v>
       </c>
       <c r="P19" t="n">
-        <v>34.02095312790698</v>
+        <v>31.97738553803527</v>
       </c>
       <c r="Q19" t="n">
-        <v>52.30409050092999</v>
+        <v>50.26052291105828</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_1_4_21</t>
+          <t>model_1_4_18</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7745985185115488</v>
+        <v>0.3747731662218098</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3297781474817481</v>
+        <v>-1.408138189912888</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9909867492262868</v>
+        <v>0.002929869754224157</v>
       </c>
       <c r="E20" t="n">
-        <v>-21.64561897895163</v>
+        <v>0.1339564488426338</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6797699277206015</v>
+        <v>0.08566422599031465</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1338080562485559</v>
+        <v>0.3711616569236482</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3978726437313524</v>
+        <v>1.429574855685539</v>
       </c>
       <c r="I20" t="n">
-        <v>0.006598588840489627</v>
+        <v>0.5615392504948307</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2784802772828275</v>
+        <v>0.8184720960627905</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1425394330616586</v>
+        <v>0.6900056732788106</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1913538029600388</v>
+        <v>0.332765060423666</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3657978352157867</v>
+        <v>0.6092303808278509</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3989293826974636</v>
+        <v>-0.6672715567418406</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3813706063668307</v>
+        <v>0.6351665794204392</v>
       </c>
       <c r="P20" t="n">
-        <v>34.02269784395079</v>
+        <v>31.98223515666179</v>
       </c>
       <c r="Q20" t="n">
-        <v>52.3058352169738</v>
+        <v>50.2653725296848</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_1_4_22</t>
+          <t>model_1_4_19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7745456755733869</v>
+        <v>0.3717031438568158</v>
       </c>
       <c r="C21" t="n">
-        <v>0.329704645786116</v>
+        <v>-1.675155179457377</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9909571548970114</v>
+        <v>-0.001248110909298328</v>
       </c>
       <c r="E21" t="n">
-        <v>-21.67057538076035</v>
+        <v>0.1234411483475197</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6794008521447943</v>
+        <v>0.07752094491295558</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1338394260993448</v>
+        <v>0.3729841548175695</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3979162775129875</v>
+        <v>1.588087675212502</v>
       </c>
       <c r="I21" t="n">
-        <v>0.006620254809383764</v>
+        <v>0.5638922445914425</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2787871739811307</v>
+        <v>0.8284097949527187</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1427037143952573</v>
+        <v>0.6961510197720806</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1913948923556916</v>
+        <v>0.3314307919284697</v>
       </c>
       <c r="M21" t="n">
-        <v>0.365840711374971</v>
+        <v>0.6107242870703354</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3987884681956986</v>
+        <v>-0.6754582830484912</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3814153078528774</v>
+        <v>0.6367240843444786</v>
       </c>
       <c r="P21" t="n">
-        <v>34.02222902054685</v>
+        <v>31.97243868124498</v>
       </c>
       <c r="Q21" t="n">
-        <v>52.30536639356986</v>
+        <v>50.25557605426799</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_1_4_23</t>
+          <t>model_1_4_20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7741448903612249</v>
+        <v>0.3717252617123864</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3287755741905337</v>
+        <v>-1.681002428161033</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9910729627147795</v>
+        <v>-0.00128070136067282</v>
       </c>
       <c r="E22" t="n">
-        <v>-21.82193205663228</v>
+        <v>0.1234378838131099</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6774053060989346</v>
+        <v>0.07750673982373679</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1340773495143039</v>
+        <v>0.3729710247030611</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3984678145459284</v>
+        <v>1.591558854630984</v>
       </c>
       <c r="I22" t="n">
-        <v>0.006535472060833719</v>
+        <v>0.563910599185651</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2806484544833152</v>
+        <v>0.828412880167449</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1435919632720745</v>
+        <v>0.69616173967655</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1914393446630818</v>
+        <v>0.3313694355058288</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3661657404978023</v>
+        <v>0.6107135373504187</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3977197076299331</v>
+        <v>-0.6753993021003029</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3817541741383707</v>
+        <v>0.63671287698673</v>
       </c>
       <c r="P22" t="n">
-        <v>34.01867682077199</v>
+        <v>31.97250908823387</v>
       </c>
       <c r="Q22" t="n">
-        <v>52.301814193795</v>
+        <v>50.25564646125688</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_1_4_20</t>
+          <t>model_1_4_21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7740316920458871</v>
+        <v>0.3715365404819091</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3127267760965358</v>
+        <v>-1.761866804084252</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9904019625309231</v>
+        <v>-0.001843340416419537</v>
       </c>
       <c r="E23" t="n">
-        <v>-21.60125191236887</v>
+        <v>0.1223965554808761</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6799018868621849</v>
+        <v>0.07664475297983053</v>
       </c>
       <c r="G23" t="n">
-        <v>0.134144548924201</v>
+        <v>0.3730830577778052</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4079950743665051</v>
+        <v>1.639563441338161</v>
       </c>
       <c r="I23" t="n">
-        <v>0.00702671039829072</v>
+        <v>0.5642274714939061</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2779346815534426</v>
+        <v>0.8293970087157581</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1424806959758667</v>
+        <v>0.6968122401048322</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1912999813709117</v>
+        <v>0.330888108446553</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3662574899223237</v>
+        <v>0.6108052535610717</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3974178454556989</v>
+        <v>-0.675902558714909</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3818498295258415</v>
+        <v>0.6368084977463493</v>
       </c>
       <c r="P23" t="n">
-        <v>34.01767467424042</v>
+        <v>31.9719084182384</v>
       </c>
       <c r="Q23" t="n">
-        <v>52.30081204726343</v>
+        <v>50.25504579126141</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_1_4_19</t>
+          <t>model_1_4_22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7740554481991547</v>
+        <v>0.3737715591778291</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3119572079583104</v>
+        <v>-2.102569455919259</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9903911623850887</v>
+        <v>0.0002809099689811134</v>
       </c>
       <c r="E24" t="n">
-        <v>-21.58661754880345</v>
+        <v>0.1293882409376629</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6800951586169383</v>
+        <v>0.08181533881249514</v>
       </c>
       <c r="G24" t="n">
-        <v>0.134130446245409</v>
+        <v>0.3717562541321266</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4084519232569683</v>
+        <v>1.841819253055648</v>
       </c>
       <c r="I24" t="n">
-        <v>0.007034617170615924</v>
+        <v>0.5630311163599024</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2777547181959674</v>
+        <v>0.8227893739805527</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1423946676832917</v>
+        <v>0.6929102451702276</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1913716568031843</v>
+        <v>0.3305274961327874</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3662382370061992</v>
+        <v>0.6097181759896343</v>
       </c>
       <c r="N24" t="n">
-        <v>0.3974811951977459</v>
+        <v>-0.6699425088591222</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3818297569732186</v>
+        <v>0.6356751410321348</v>
       </c>
       <c r="P24" t="n">
-        <v>34.0178849462234</v>
+        <v>31.97903374058828</v>
       </c>
       <c r="Q24" t="n">
-        <v>52.30102231924641</v>
+        <v>50.26217111361129</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_1_4_17</t>
+          <t>model_1_4_23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7925335447997894</v>
+        <v>0.3750645106418308</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3064829964787742</v>
+        <v>-2.450844104351171</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9936686358104101</v>
+        <v>0.001342780948078715</v>
       </c>
       <c r="E25" t="n">
-        <v>-15.07508515224898</v>
+        <v>0.1334983388470219</v>
       </c>
       <c r="F25" t="n">
-        <v>0.772738250481132</v>
+        <v>0.08478516055916518</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1231610498910613</v>
+        <v>0.3709887022905001</v>
       </c>
       <c r="H25" t="n">
-        <v>0.411701651664844</v>
+        <v>2.048570129046279</v>
       </c>
       <c r="I25" t="n">
-        <v>0.00463518325800362</v>
+        <v>0.5624330819632871</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1976803625771593</v>
+        <v>0.8189050422441166</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1011577729175814</v>
+        <v>0.6906690621037019</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1857698932699277</v>
+        <v>0.330626865868075</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3509430863987227</v>
+        <v>0.6090884191071935</v>
       </c>
       <c r="N25" t="n">
-        <v>0.4467561194661052</v>
+        <v>-0.6664946382884511</v>
       </c>
       <c r="O25" t="n">
-        <v>0.3658834601390551</v>
+        <v>0.6350185740954321</v>
       </c>
       <c r="P25" t="n">
-        <v>34.18852486270282</v>
+        <v>31.98316733777109</v>
       </c>
       <c r="Q25" t="n">
-        <v>52.47166223572583</v>
+        <v>50.2663047107941</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_1_4_18</t>
+          <t>model_1_4_24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7829696543664229</v>
+        <v>0.3755459047375564</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3016119701667189</v>
+        <v>-2.490975198634847</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9921195898616224</v>
+        <v>0.001558059827536429</v>
       </c>
       <c r="E26" t="n">
-        <v>-18.48790751637277</v>
+        <v>0.1348918138657792</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7243209500906233</v>
+        <v>0.08573803286136772</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1288385883908627</v>
+        <v>0.3707029259601352</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4145933033010604</v>
+        <v>2.072393680186076</v>
       </c>
       <c r="I26" t="n">
-        <v>0.005769237725997206</v>
+        <v>0.5623118391971557</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2396489093040824</v>
+        <v>0.8175881102978084</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1227090735150398</v>
+        <v>0.689949974747482</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1893608427278304</v>
+        <v>0.3303858786247251</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3589409260461429</v>
+        <v>0.6088537804433304</v>
       </c>
       <c r="N26" t="n">
-        <v>0.4212524116437943</v>
+        <v>-0.6652109206998493</v>
       </c>
       <c r="O26" t="n">
-        <v>0.3742217843780765</v>
+        <v>0.6347739463778794</v>
       </c>
       <c r="P26" t="n">
-        <v>34.09838982174971</v>
+        <v>31.98470855157813</v>
       </c>
       <c r="Q26" t="n">
-        <v>52.38152719477272</v>
+        <v>50.26784592460114</v>
       </c>
     </row>
   </sheetData>
